--- a/docs/design-sample/DD04_コード定義書.xlsx
+++ b/docs/design-sample/DD04_コード定義書.xlsx
@@ -720,7 +720,7 @@
       <c r="V25" s="5" t="n"/>
       <c r="W25" s="5" t="n"/>
       <c r="X25" s="8" t="n">
-        <v>46307</v>
+        <v>46296</v>
       </c>
       <c r="Y25" s="7" t="n"/>
       <c r="Z25" s="7" t="n"/>
@@ -1050,7 +1050,7 @@
       <c r="AL2" s="5" t="n"/>
       <c r="AM2" s="6" t="inlineStr">
         <is>
-          <t>佐藤 花子</t>
+          <t>山田 太郎</t>
         </is>
       </c>
       <c r="AN2" s="7" t="n"/>
@@ -1069,7 +1069,7 @@
       <c r="AW2" s="5" t="n"/>
       <c r="AX2" s="5" t="n"/>
       <c r="AY2" s="8" t="n">
-        <v>46307</v>
+        <v>46296</v>
       </c>
       <c r="AZ2" s="7" t="n"/>
       <c r="BA2" s="7" t="n"/>
@@ -1485,7 +1485,7 @@
       <c r="AL2" s="5" t="n"/>
       <c r="AM2" s="6" t="inlineStr">
         <is>
-          <t>佐藤 花子</t>
+          <t>山田 太郎</t>
         </is>
       </c>
       <c r="AN2" s="7" t="n"/>
@@ -1504,7 +1504,7 @@
       <c r="AW2" s="5" t="n"/>
       <c r="AX2" s="5" t="n"/>
       <c r="AY2" s="8" t="n">
-        <v>46307</v>
+        <v>46296</v>
       </c>
       <c r="AZ2" s="7" t="n"/>
       <c r="BA2" s="7" t="n"/>
